--- a/output/第10期計画_給付実績データの受領点検.xlsx
+++ b/output/第10期計画_給付実績データの受領点検.xlsx
@@ -218,9 +218,6 @@
     <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -231,6 +228,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -828,7 +828,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>【4　令和7年度の集計が一致しません（ご確認をお願いします）】</t>
+          <t>【4　令和7年度の集計の差（令和8年9月25日に解決しました）】</t>
         </is>
       </c>
     </row>
@@ -839,8 +839,9 @@
 　令和6年度　3町計 3,084,937,834円＝大雪 3,084,937,834円（差0）
 　令和7年度　3町計 3,213,054,558円－大雪 3,083,474,291円＝＋129,580,267円（＋4.20％）
 　令和8年度　3町計 1,110,075,123円＝大雪 1,110,075,123円（差0）
-令和6年度と令和8年度は完全に一致する一方、令和7年度のみ3町の合計が大雪地区広域連合を1億2,958万円上回ります。受託者の側では原因を特定できません。
-【美瑛町】令和7年度のファイルは、利用回数のシート名が他年度と異なる（「（東神楽）」となっている）ため、他年度とは異なる手順で作成された可能性があります。
+令和6年度と令和8年度は完全に一致する一方、令和7年度のみ3町の合計が大雪地区広域連合を1億2,958万円上回っていました。
+【令和8年9月25日】令和7年度の広域連合単位のファイルの再提供を受け、「介護度別給付費」の表の総計が3,213,054,558円となり、要支援1から要介護5までの全7区分で3町合計と円単位で一致しました。従前のファイルもその明細を集計すると同じ額になるため、差は抽出条件の違いではなく表が明細と一致していなかったことによるものです。
+【美瑛町】令和7年度のファイルは、利用回数のシート名が他年度と異なる（「（東神楽）」となっている）ものの、収録されている値は美瑛町のものであることを確認しており、シート名の誤りとして扱います。
 令和7年度について、【大雪】と【美瑛町】のいずれかのファイルの再作成をご検討いただけますでしょうか。解消するまでは、令和7年度の町別の値は用いず、大雪地区広域連合の合計のみを用います。</t>
         </is>
       </c>
@@ -1039,16 +1040,16 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>109102148</v>
+        <v>115258140</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>1161111101</v>
+        <v>1202796288</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>1813261042</v>
+        <v>1895000130</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>3083474291</v>
+        <v>3213054558</v>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
@@ -1247,13 +1248,13 @@
         </is>
       </c>
       <c r="B19" s="11" t="n">
-        <v>28268</v>
+        <v>29456</v>
       </c>
       <c r="C19" s="11" t="n">
         <v>26885</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>1383</v>
+        <v>2571</v>
       </c>
       <c r="E19" s="5" t="inlineStr"/>
       <c r="F19" s="5" t="inlineStr">
@@ -1348,12 +1349,12 @@
       <c r="D25" s="11" t="n">
         <v>848457073</v>
       </c>
-      <c r="E25" s="19" t="n">
-        <v>129580267</v>
+      <c r="E25" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>3町計が大雪を129,580,267円（+4.20％）上回ります。原因を特定できていません（00シート4）。</t>
+          <t>一致します。</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4179,7 @@
           <t>決定1（人口推計の基礎）・決定2（認定率のシナリオ）</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>令和8年9月</t>
         </is>
@@ -4203,7 +4204,7 @@
           <t>上記に加え資料No.9（決算・基金）、国の政令改正の告示</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr">
+      <c r="E6" s="19" t="inlineStr">
         <is>
           <t>令和8年12月</t>
         </is>
@@ -4228,7 +4229,7 @@
           <t>分母の定義のご決定</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t>ご決定後</t>
         </is>
@@ -4253,7 +4254,7 @@
           <t>年報（資料No.21）の受領</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>令和8年9月</t>
         </is>
@@ -4278,7 +4279,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="E9" s="19" t="inlineStr">
         <is>
           <t>令和8年9月</t>
         </is>
@@ -4303,7 +4304,7 @@
           <t>上記1の完了</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
+      <c r="E10" s="19" t="inlineStr">
         <is>
           <t>令和8年10月</t>
         </is>
@@ -4328,7 +4329,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>反映済み</t>
         </is>
@@ -4602,22 +4603,22 @@
       <c r="F11" s="5" t="inlineStr"/>
     </row>
     <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>3町計</t>
         </is>
       </c>
-      <c r="B12" s="23" t="n">
+      <c r="B12" s="22" t="n">
         <v>1994</v>
       </c>
-      <c r="C12" s="23" t="n">
+      <c r="C12" s="22" t="n">
         <v>2029</v>
       </c>
-      <c r="D12" s="23" t="n">
+      <c r="D12" s="22" t="n">
         <v>2014</v>
       </c>
-      <c r="E12" s="22" t="inlineStr"/>
-      <c r="F12" s="22" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr"/>
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t>見える化B系列による第1号認定者1,984人（令和8年3月末）と近い水準です。定義の対応は別途確認します。</t>
         </is>
@@ -4691,7 +4692,7 @@
       <c r="B17" s="11" t="n">
         <v>6178624</v>
       </c>
-      <c r="C17" s="19" t="n">
+      <c r="C17" s="23" t="n">
         <v>471272</v>
       </c>
       <c r="D17" s="11" t="n">
@@ -4715,7 +4716,7 @@
       <c r="B18" s="11" t="n">
         <v>50986</v>
       </c>
-      <c r="C18" s="19" t="n">
+      <c r="C18" s="23" t="n">
         <v>18492717</v>
       </c>
       <c r="D18" s="11" t="n">
@@ -5036,7 +5037,7 @@
           <t>125項目である。被保険者・認定・事業所・サービス種類・日数回数・単位数・請求額・公費・食事提供費・特定入所者介護サービス費・社会福祉法人軽減までを収録している。最も細かい単位はサービス種類コード（第39列）であり、サービス項目コード（加算・減算の単位）の列はない。</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>サービス種類単位</t>
         </is>
